--- a/教育（きょういく）.xlsx
+++ b/教育（きょういく）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="教育（きょういく）" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="291">
   <si>
     <t>教育</t>
   </si>
@@ -658,6 +658,12 @@
     <t>ひょうげん</t>
   </si>
   <si>
+    <t>母校</t>
+  </si>
+  <si>
+    <t>ぼこう</t>
+  </si>
+  <si>
     <t>卒業証書</t>
   </si>
   <si>
@@ -965,7 +971,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,13 +990,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1446,148 +1445,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2552,250 +2551,256 @@
       <c r="H22" s="1" t="s">
         <v>189</v>
       </c>
+      <c r="J22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="23" ht="18" spans="1:12">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:12">
       <c r="A27" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:12">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:12">
       <c r="A30" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:12">
       <c r="A31" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:12">
       <c r="A32" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G35" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H35" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G36" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G37" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" t="s">
         <v>253</v>
-      </c>
-      <c r="G37" t="s">
-        <v>254</v>
-      </c>
-      <c r="H37" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G38" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H38" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -2815,26 +2820,26 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2856,63 +2861,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>29</v>
@@ -2920,42 +2925,42 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/教育（きょういく）.xlsx
+++ b/教育（きょういく）.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="293">
   <si>
     <t>教育</t>
   </si>
@@ -170,34 +170,64 @@
     <t>さずける</t>
   </si>
   <si>
+    <t>教材</t>
+  </si>
+  <si>
+    <t>きょうざい</t>
+  </si>
+  <si>
+    <t>理工</t>
+  </si>
+  <si>
+    <t>りこう</t>
+  </si>
+  <si>
+    <t>交換</t>
+  </si>
+  <si>
+    <t>こうかん</t>
+  </si>
+  <si>
+    <t>早退</t>
+  </si>
+  <si>
+    <t>そうたい</t>
+  </si>
+  <si>
+    <t>感じる</t>
+  </si>
+  <si>
+    <t>かんじる</t>
+  </si>
+  <si>
     <t>宿題</t>
   </si>
   <si>
     <t>しゅくだい</t>
   </si>
   <si>
-    <t>理工</t>
-  </si>
-  <si>
-    <t>りこう</t>
-  </si>
-  <si>
-    <t>交換</t>
-  </si>
-  <si>
-    <t>こうかん</t>
-  </si>
-  <si>
-    <t>早退</t>
-  </si>
-  <si>
-    <t>そうたい</t>
-  </si>
-  <si>
-    <t>感じる</t>
-  </si>
-  <si>
-    <t>かんじる</t>
+    <t>数学</t>
+  </si>
+  <si>
+    <t>すうがく</t>
+  </si>
+  <si>
+    <t>経歴</t>
+  </si>
+  <si>
+    <t>けいれき</t>
+  </si>
+  <si>
+    <t>遅刻早退</t>
+  </si>
+  <si>
+    <t>ちこくそうたい</t>
+  </si>
+  <si>
+    <t>存じる</t>
+  </si>
+  <si>
+    <t>ぞんじる</t>
   </si>
   <si>
     <t>論文</t>
@@ -206,67 +236,37 @@
     <t>ろんぶん</t>
   </si>
   <si>
-    <t>数学</t>
-  </si>
-  <si>
-    <t>すうがく</t>
-  </si>
-  <si>
-    <t>経歴</t>
-  </si>
-  <si>
-    <t>けいれき</t>
-  </si>
-  <si>
-    <t>遅刻早退</t>
-  </si>
-  <si>
-    <t>ちこくそうたい</t>
-  </si>
-  <si>
-    <t>存じる</t>
-  </si>
-  <si>
-    <t>ぞんじる</t>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>ぶつり</t>
+  </si>
+  <si>
+    <t>経験</t>
+  </si>
+  <si>
+    <t>けいけん</t>
+  </si>
+  <si>
+    <t>喧嘩</t>
+  </si>
+  <si>
+    <t>けんか</t>
+  </si>
+  <si>
+    <t>受け付ける</t>
+  </si>
+  <si>
+    <t>うけつける</t>
+  </si>
+  <si>
+    <t>（接受）</t>
   </si>
   <si>
     <t>試験</t>
   </si>
   <si>
     <t>しけん</t>
-  </si>
-  <si>
-    <t>物理</t>
-  </si>
-  <si>
-    <t>ぶつり</t>
-  </si>
-  <si>
-    <t>経験</t>
-  </si>
-  <si>
-    <t>けいけん</t>
-  </si>
-  <si>
-    <t>喧嘩</t>
-  </si>
-  <si>
-    <t>けんか</t>
-  </si>
-  <si>
-    <t>受け付ける</t>
-  </si>
-  <si>
-    <t>うけつける</t>
-  </si>
-  <si>
-    <t>（接受）</t>
-  </si>
-  <si>
-    <t>受験</t>
-  </si>
-  <si>
-    <t>じゅけん</t>
   </si>
   <si>
     <t>機械</t>
@@ -322,28 +322,52 @@
     </r>
   </si>
   <si>
+    <t>受験</t>
+  </si>
+  <si>
+    <t>じゅけん</t>
+  </si>
+  <si>
+    <t>土木</t>
+  </si>
+  <si>
+    <t>どぼく</t>
+  </si>
+  <si>
+    <t>結果</t>
+  </si>
+  <si>
+    <t>けっか</t>
+  </si>
+  <si>
+    <t>入学式</t>
+  </si>
+  <si>
+    <t>にゅうがくしき</t>
+  </si>
+  <si>
     <t>授業</t>
   </si>
   <si>
     <t>じゅぎょう</t>
   </si>
   <si>
-    <t>土木</t>
-  </si>
-  <si>
-    <t>どぼく</t>
-  </si>
-  <si>
-    <t>結果</t>
-  </si>
-  <si>
-    <t>けっか</t>
-  </si>
-  <si>
-    <t>入学式</t>
-  </si>
-  <si>
-    <t>にゅうがくしき</t>
+    <t>計算機</t>
+  </si>
+  <si>
+    <t>けいさんき</t>
+  </si>
+  <si>
+    <t>効果</t>
+  </si>
+  <si>
+    <t>こうか</t>
+  </si>
+  <si>
+    <t>卒業</t>
+  </si>
+  <si>
+    <t>そつぎょう</t>
   </si>
   <si>
     <t>練習</t>
@@ -352,22 +376,22 @@
     <t>れんしゅう</t>
   </si>
   <si>
-    <t>計算機</t>
-  </si>
-  <si>
-    <t>けいさんき</t>
-  </si>
-  <si>
-    <t>効果</t>
-  </si>
-  <si>
-    <t>こうか</t>
-  </si>
-  <si>
-    <t>卒業</t>
-  </si>
-  <si>
-    <t>そつぎょう</t>
+    <t>化学、科学</t>
+  </si>
+  <si>
+    <t>かがく</t>
+  </si>
+  <si>
+    <t>思考</t>
+  </si>
+  <si>
+    <t>しこう</t>
+  </si>
+  <si>
+    <t>卒業式</t>
+  </si>
+  <si>
+    <t>そつぎょうしき</t>
   </si>
   <si>
     <t>準備</t>
@@ -376,22 +400,22 @@
     <t>じゅんび</t>
   </si>
   <si>
-    <t>化学、科学</t>
-  </si>
-  <si>
-    <t>かがく</t>
-  </si>
-  <si>
-    <t>思考</t>
-  </si>
-  <si>
-    <t>しこう</t>
-  </si>
-  <si>
-    <t>卒業式</t>
-  </si>
-  <si>
-    <t>そつぎょうしき</t>
+    <t>医学</t>
+  </si>
+  <si>
+    <t>いがく</t>
+  </si>
+  <si>
+    <t>考慮</t>
+  </si>
+  <si>
+    <t>こうりょ</t>
+  </si>
+  <si>
+    <t>議論</t>
+  </si>
+  <si>
+    <t>ぎろん</t>
   </si>
   <si>
     <t>予備</t>
@@ -400,22 +424,22 @@
     <t>よび</t>
   </si>
   <si>
-    <t>医学</t>
-  </si>
-  <si>
-    <t>いがく</t>
-  </si>
-  <si>
-    <t>考慮</t>
-  </si>
-  <si>
-    <t>こうりょ</t>
-  </si>
-  <si>
-    <t>議論</t>
-  </si>
-  <si>
-    <t>ぎろん</t>
+    <t>環境</t>
+  </si>
+  <si>
+    <t>かんきょう</t>
+  </si>
+  <si>
+    <t>分析</t>
+  </si>
+  <si>
+    <t>ぶんせき</t>
+  </si>
+  <si>
+    <t>登校</t>
+  </si>
+  <si>
+    <t>とうこう</t>
   </si>
   <si>
     <t>予備校</t>
@@ -424,22 +448,22 @@
     <t>よびこう</t>
   </si>
   <si>
-    <t>環境</t>
-  </si>
-  <si>
-    <t>かんきょう</t>
-  </si>
-  <si>
-    <t>分析</t>
-  </si>
-  <si>
-    <t>ぶんせき</t>
-  </si>
-  <si>
-    <t>登校</t>
-  </si>
-  <si>
-    <t>とうこう</t>
+    <t>生物</t>
+  </si>
+  <si>
+    <t>せいぶつ</t>
+  </si>
+  <si>
+    <t>理解</t>
+  </si>
+  <si>
+    <t>りかい</t>
+  </si>
+  <si>
+    <t>通学</t>
+  </si>
+  <si>
+    <t>つうがく</t>
   </si>
   <si>
     <t>資料</t>
@@ -448,22 +472,22 @@
     <t>しりょう</t>
   </si>
   <si>
-    <t>生物</t>
-  </si>
-  <si>
-    <t>せいぶつ</t>
-  </si>
-  <si>
-    <t>理解</t>
-  </si>
-  <si>
-    <t>りかい</t>
-  </si>
-  <si>
-    <t>通学</t>
-  </si>
-  <si>
-    <t>つうがく</t>
+    <t>地理</t>
+  </si>
+  <si>
+    <t>ちり</t>
+  </si>
+  <si>
+    <t>推論</t>
+  </si>
+  <si>
+    <t>すいろん</t>
+  </si>
+  <si>
+    <t>下校</t>
+  </si>
+  <si>
+    <t>げこう</t>
   </si>
   <si>
     <t>書物</t>
@@ -472,22 +496,22 @@
     <t>しょもつ</t>
   </si>
   <si>
-    <t>地理</t>
-  </si>
-  <si>
-    <t>ちり</t>
-  </si>
-  <si>
-    <t>推論</t>
-  </si>
-  <si>
-    <t>すいろん</t>
-  </si>
-  <si>
-    <t>下校</t>
-  </si>
-  <si>
-    <t>げこう</t>
+    <t>経済</t>
+  </si>
+  <si>
+    <t>けいざい</t>
+  </si>
+  <si>
+    <t>完成</t>
+  </si>
+  <si>
+    <t>かんせい</t>
+  </si>
+  <si>
+    <t>放課</t>
+  </si>
+  <si>
+    <t>ほうか</t>
   </si>
   <si>
     <t>勉強</t>
@@ -496,22 +520,22 @@
     <t>べんきょう</t>
   </si>
   <si>
-    <t>経済</t>
-  </si>
-  <si>
-    <t>けいざい</t>
-  </si>
-  <si>
-    <t>完成</t>
-  </si>
-  <si>
-    <t>かんせい</t>
-  </si>
-  <si>
-    <t>放課</t>
-  </si>
-  <si>
-    <t>ほうか</t>
+    <t>管理</t>
+  </si>
+  <si>
+    <t>かんり</t>
+  </si>
+  <si>
+    <t>矛盾</t>
+  </si>
+  <si>
+    <t>むじゅん</t>
+  </si>
+  <si>
+    <t>合唱</t>
+  </si>
+  <si>
+    <t>がっしょう</t>
   </si>
   <si>
     <t>成績</t>
@@ -520,22 +544,22 @@
     <t>せいせき</t>
   </si>
   <si>
-    <t>管理</t>
-  </si>
-  <si>
-    <t>かんり</t>
-  </si>
-  <si>
-    <t>矛盾</t>
-  </si>
-  <si>
-    <t>むじゅん</t>
-  </si>
-  <si>
-    <t>合唱</t>
-  </si>
-  <si>
-    <t>がっしょう</t>
+    <t>政治</t>
+  </si>
+  <si>
+    <t>せいじ</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>くぶん</t>
+  </si>
+  <si>
+    <t>文化祭</t>
+  </si>
+  <si>
+    <t>ぶんかさい</t>
   </si>
   <si>
     <t>研究</t>
@@ -544,22 +568,22 @@
     <t>けんきゅう</t>
   </si>
   <si>
-    <t>政治</t>
-  </si>
-  <si>
-    <t>せいじ</t>
-  </si>
-  <si>
-    <t>区分</t>
-  </si>
-  <si>
-    <t>くぶん</t>
-  </si>
-  <si>
-    <t>文化祭</t>
-  </si>
-  <si>
-    <t>ぶんかさい</t>
+    <t>歴史</t>
+  </si>
+  <si>
+    <t>れきし</t>
+  </si>
+  <si>
+    <t>区別</t>
+  </si>
+  <si>
+    <t>くべつ</t>
+  </si>
+  <si>
+    <t>欠席</t>
+  </si>
+  <si>
+    <t>けっせき</t>
   </si>
   <si>
     <t>専攻</t>
@@ -568,22 +592,22 @@
     <t>せんこう</t>
   </si>
   <si>
-    <t>歴史</t>
-  </si>
-  <si>
-    <t>れきし</t>
-  </si>
-  <si>
-    <t>区別</t>
-  </si>
-  <si>
-    <t>くべつ</t>
-  </si>
-  <si>
-    <t>欠席</t>
-  </si>
-  <si>
-    <t>けっせき</t>
+    <t>英語</t>
+  </si>
+  <si>
+    <t>えいご</t>
+  </si>
+  <si>
+    <t>結論</t>
+  </si>
+  <si>
+    <t>けつろん</t>
+  </si>
+  <si>
+    <t>欠席者</t>
+  </si>
+  <si>
+    <t>けっせきしゃ</t>
   </si>
   <si>
     <t>指導</t>
@@ -592,22 +616,25 @@
     <t>しどう</t>
   </si>
   <si>
-    <t>英語</t>
-  </si>
-  <si>
-    <t>えいご</t>
-  </si>
-  <si>
-    <t>結論</t>
-  </si>
-  <si>
-    <t>けつろん</t>
-  </si>
-  <si>
-    <t>欠席者</t>
-  </si>
-  <si>
-    <t>けっせきしゃ</t>
+    <t>国語</t>
+  </si>
+  <si>
+    <t>こくご</t>
+  </si>
+  <si>
+    <t>列挙</t>
+  </si>
+  <si>
+    <t>れっきょ</t>
+  </si>
+  <si>
+    <t>虐め、苛め</t>
+  </si>
+  <si>
+    <t>いじめ</t>
+  </si>
+  <si>
+    <t>（霸凌）</t>
   </si>
   <si>
     <t>問題</t>
@@ -616,25 +643,22 @@
     <t>もんだい</t>
   </si>
   <si>
-    <t>国語</t>
-  </si>
-  <si>
-    <t>こくご</t>
-  </si>
-  <si>
-    <t>列挙</t>
-  </si>
-  <si>
-    <t>れっきょ</t>
-  </si>
-  <si>
-    <t>虐め、苛め</t>
-  </si>
-  <si>
-    <t>いじめ</t>
-  </si>
-  <si>
-    <t>（霸凌）</t>
+    <t>哲学</t>
+  </si>
+  <si>
+    <t>てつがく</t>
+  </si>
+  <si>
+    <t>表現</t>
+  </si>
+  <si>
+    <t>ひょうげん</t>
+  </si>
+  <si>
+    <t>母校</t>
+  </si>
+  <si>
+    <t>ぼこう</t>
   </si>
   <si>
     <t>題目</t>
@@ -646,22 +670,16 @@
     <t>進路指導｜しんろしどう</t>
   </si>
   <si>
-    <t>哲学</t>
-  </si>
-  <si>
-    <t>てつがく</t>
-  </si>
-  <si>
-    <t>表現</t>
-  </si>
-  <si>
-    <t>ひょうげん</t>
-  </si>
-  <si>
-    <t>母校</t>
-  </si>
-  <si>
-    <t>ぼこう</t>
+    <t>情報</t>
+  </si>
+  <si>
+    <t>じょうほう</t>
+  </si>
+  <si>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>ひょうじ</t>
   </si>
   <si>
     <t>卒業証書</t>
@@ -670,16 +688,16 @@
     <t>そつぎょうしょうしょ</t>
   </si>
   <si>
-    <t>情報</t>
-  </si>
-  <si>
-    <t>じょうほう</t>
-  </si>
-  <si>
-    <t>表示</t>
-  </si>
-  <si>
-    <t>ひょうじ</t>
+    <t>体育</t>
+  </si>
+  <si>
+    <t>たいいく</t>
+  </si>
+  <si>
+    <t>規則</t>
+  </si>
+  <si>
+    <t>きそく</t>
   </si>
   <si>
     <t>進路</t>
@@ -691,31 +709,25 @@
     <t>（年级）</t>
   </si>
   <si>
-    <t>体育</t>
-  </si>
-  <si>
-    <t>たいいく</t>
-  </si>
-  <si>
-    <t>規則</t>
-  </si>
-  <si>
-    <t>きそく</t>
+    <t>科目</t>
+  </si>
+  <si>
+    <t>かもく</t>
+  </si>
+  <si>
+    <t>立場</t>
+  </si>
+  <si>
+    <t>たちば</t>
   </si>
   <si>
     <t>機会</t>
   </si>
   <si>
-    <t>科目</t>
-  </si>
-  <si>
-    <t>かもく</t>
-  </si>
-  <si>
-    <t>立場</t>
-  </si>
-  <si>
-    <t>たちば</t>
+    <t>計画</t>
+  </si>
+  <si>
+    <t>けいかく</t>
   </si>
   <si>
     <t>年生</t>
@@ -724,10 +736,10 @@
     <t>ねんせい</t>
   </si>
   <si>
-    <t>計画</t>
-  </si>
-  <si>
-    <t>けいかく</t>
+    <t>参加</t>
+  </si>
+  <si>
+    <t>さんか</t>
   </si>
   <si>
     <t>義務</t>
@@ -736,10 +748,10 @@
     <t>ぎむ</t>
   </si>
   <si>
-    <t>参加</t>
-  </si>
-  <si>
-    <t>さんか</t>
+    <t>参考</t>
+  </si>
+  <si>
+    <t>さんこう</t>
   </si>
   <si>
     <t>義務教育</t>
@@ -748,10 +760,10 @@
     <t>ぎむきょういく</t>
   </si>
   <si>
-    <t>参考</t>
-  </si>
-  <si>
-    <t>さんこう</t>
+    <t>交流</t>
+  </si>
+  <si>
+    <t>こうりゅう</t>
   </si>
   <si>
     <t>研修</t>
@@ -760,10 +772,10 @@
     <t>けんしゅう</t>
   </si>
   <si>
-    <t>交流</t>
-  </si>
-  <si>
-    <t>こうりゅう</t>
+    <t>理念</t>
+  </si>
+  <si>
+    <t>りねん</t>
   </si>
   <si>
     <t>研修旅行</t>
@@ -772,10 +784,10 @@
     <t>けんしゅうりょこう</t>
   </si>
   <si>
-    <t>理念</t>
-  </si>
-  <si>
-    <t>りねん</t>
+    <t>概念</t>
+  </si>
+  <si>
+    <t>がいねん</t>
   </si>
   <si>
     <t>基金</t>
@@ -784,19 +796,22 @@
     <t>ききん</t>
   </si>
   <si>
-    <t>概念</t>
-  </si>
-  <si>
-    <t>がいねん</t>
+    <t>了解</t>
+  </si>
+  <si>
+    <t>りょうかい</t>
   </si>
   <si>
     <t>掛金</t>
   </si>
   <si>
-    <t>了解</t>
-  </si>
-  <si>
-    <t>りょうかい</t>
+    <t>検討</t>
+  </si>
+  <si>
+    <t>けんとう</t>
+  </si>
+  <si>
+    <t>（探讨，讨论）</t>
   </si>
   <si>
     <t>要領</t>
@@ -805,13 +820,10 @@
     <t>ようりょう</t>
   </si>
   <si>
-    <t>検討</t>
-  </si>
-  <si>
-    <t>けんとう</t>
-  </si>
-  <si>
-    <t>（探讨，讨论）</t>
+    <t>討論</t>
+  </si>
+  <si>
+    <t>とうろん</t>
   </si>
   <si>
     <t>必修</t>
@@ -820,10 +832,10 @@
     <t>ひっしゅう</t>
   </si>
   <si>
-    <t>討論</t>
-  </si>
-  <si>
-    <t>とうろん</t>
+    <t>取得</t>
+  </si>
+  <si>
+    <t>しゅとく</t>
   </si>
   <si>
     <t>必修科目</t>
@@ -832,10 +844,10 @@
     <t>ひっしゅうかもく</t>
   </si>
   <si>
-    <t>取得</t>
-  </si>
-  <si>
-    <t>しゅとく</t>
+    <t>習得</t>
+  </si>
+  <si>
+    <t>しゅうとく</t>
   </si>
   <si>
     <t>教科書</t>
@@ -844,10 +856,7 @@
     <t>きょうかしょ</t>
   </si>
   <si>
-    <t>習得</t>
-  </si>
-  <si>
-    <t>しゅうとく</t>
+    <t>修得</t>
   </si>
   <si>
     <t>育成</t>
@@ -856,19 +865,16 @@
     <t>いくせい</t>
   </si>
   <si>
-    <t>修得</t>
+    <t>落第</t>
+  </si>
+  <si>
+    <t>らくだい</t>
   </si>
   <si>
     <t>博士</t>
   </si>
   <si>
     <t>はかせ</t>
-  </si>
-  <si>
-    <t>落第</t>
-  </si>
-  <si>
-    <t>らくだい</t>
   </si>
   <si>
     <t>回答</t>
@@ -1913,7 +1919,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:R38"/>
+  <dimension ref="A2:R39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -2044,10 +2050,10 @@
       </c>
     </row>
     <row r="5" ht="18" spans="1:18">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2080,7 +2086,7 @@
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2536,33 +2542,33 @@
       <c r="B22" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="J22" t="s">
         <v>189</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>190</v>
       </c>
-      <c r="K22" t="s">
+    </row>
+    <row r="23" ht="18" spans="1:12">
+      <c r="A23" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="23" ht="18" spans="1:12">
-      <c r="A23" t="s">
+      <c r="B23" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>193</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -2579,54 +2585,54 @@
       </c>
     </row>
     <row r="24" ht="18" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>198</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:12">
       <c r="A25" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>70</v>
+      <c r="C25" t="s">
+        <v>206</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>212</v>
@@ -2636,7 +2642,7 @@
       </c>
     </row>
     <row r="27" ht="18" spans="1:12">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>214</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2664,7 +2670,7 @@
       </c>
     </row>
     <row r="29" ht="18" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>222</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2709,18 +2715,18 @@
       <c r="A32" s="1" t="s">
         <v>234</v>
       </c>
+      <c r="B32" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="G32" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:9">
-      <c r="A33" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>238</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2734,10 +2740,10 @@
       </c>
     </row>
     <row r="34" ht="18" spans="1:9">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>243</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -2801,6 +2807,14 @@
       </c>
       <c r="H38" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="39" ht="18" spans="1:9">
+      <c r="A39" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2820,26 +2834,26 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -2861,63 +2875,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>29</v>
@@ -2925,42 +2939,42 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/教育（きょういく）.xlsx
+++ b/教育（きょういく）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22320" windowHeight="9144" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="教育（きょういく）" sheetId="2" r:id="rId1"/>
